--- a/human_resources_forms/005_employee_engagement_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/005_employee_engagement_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Welcome to the Employee Engagement Survey. This survey aims to measure employee engagement and satisfaction.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>tenure</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How many years have you been with the company?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide the number of years you've worked for the company.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
+          <t>job_satisfaction</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How satisfied are you with your job?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Scale - 1-5, where 1 is 'very dissatisfied' and 5 is 'very satisfied'.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>decision_making</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often do you feel empowered to make decisions?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select one option - Never, Rarely, Sometimes, Often, Almost Always</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
+          <t>work_challenges</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What are the most significant challenges you face at work?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide a brief description.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>work_hours</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How many hours do you usually work per week?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter a number.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,20 +677,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
+          <t>benefits</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Which of the following benefits do you value most?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>manager_leadership</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How would you rate your manager's leadership style?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select one option - Autocratic, Democratic, Laissez-Faire, Participative, Transformational</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
+          <t>work_life_balance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Are you satisfied with your work-life balance?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select one option - Yes, No</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>open_ended_feedback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What would you like to see improved in the workplace?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide a brief description.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How likely are you to recommend this organization to a friend or family member?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select one option - Very Likely, Not Likely, Not Likely at all</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>communication_method</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is your preferred mode of communication with your team?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select all that apply</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
+          <t>company_culture</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>How would you rate the company culture?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select one option - Very Positive, Positive, Neutral, Negative, Very Negative</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,269 +871,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>conclusion</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Thank you for participating in this survey. Your input is greatly appreciated.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>This concludes the survey.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>first_page</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>how_satisfied</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +901,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,272 +929,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>decision_making_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>health_insurance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Health Insurance</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>retirement_plan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Retirement Plan</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>paid_time_off</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Paid Time Off</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>stock_options</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Stock Options</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>manager_leadership_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>autocratic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Autocratic</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>manager_leadership_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>democratic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Democratic</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>manager_leadership_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>laissez-faire</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Laissez-Faire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>manager_leadership_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>participative</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Participative</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>manager_leadership_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>transformational</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Transformational</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>how_satisfied_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>work_life_balance_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>recommendation_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>very_likely</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Very Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>recommendation_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>not_likely</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not Likely</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>recommendation_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>not_likely_at_all</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not Likely at all</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>communication_method_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>communication_method_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>phone_call</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Phone Call</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>communication_method_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>text_message</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Text Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>communication_method_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>instant_messaging</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Instant Messaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>communication_method_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>company_culture_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>very_positive</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Very Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>company_culture_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>positive</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>company_culture_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>company_culture_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>company_culture_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>very_negative</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Very Negative</t>
         </is>
       </c>
     </row>
